--- a/Assets/Scripts/Core/Parser/vfx.xlsx
+++ b/Assets/Scripts/Core/Parser/vfx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Documents\Idle_RPG_2\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335BC0AB-E106-4D9F-BC58-B7353F5DF88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424A457D-6C47-4122-A4DD-FC8EF2A632C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5685" yWindow="1695" windowWidth="21600" windowHeight="13785" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5475" yWindow="1095" windowWidth="21600" windowHeight="13785" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pooling" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t>fileName</t>
   </si>
@@ -71,15 +71,6 @@
   </si>
   <si>
     <t>Slash_Attack</t>
-  </si>
-  <si>
-    <t>Slash</t>
-  </si>
-  <si>
-    <t>exclusive</t>
-  </si>
-  <si>
-    <t>Slash2</t>
   </si>
 </sst>
 </file>
@@ -4122,34 +4113,22 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="str">
         <f>IF(NonPooling!$B2="", "", _xlfn.BITOR(NonPooling!$B2, 3221225472))</f>
-        <v>3221225473</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
+        <v/>
+      </c>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="str">
         <f>IF(NonPooling!$B3="", "", _xlfn.BITOR(NonPooling!$B3, 3221225472))</f>
-        <v>3221225474</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>14</v>
-      </c>
+        <v/>
+      </c>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1"/>
